--- a/data/credit_bond_all_2026-09-10.xlsx
+++ b/data/credit_bond_all_2026-09-10.xlsx
@@ -945,8 +945,12 @@
           <t>1.40 ~ 2.40</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>54.94</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.80</t>
@@ -1177,8 +1181,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>48.74</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.91</t>
@@ -1407,8 +1415,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>48.94</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -1639,8 +1651,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>18.74</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>1.66</t>
@@ -1869,8 +1885,12 @@
           <t>1.30 ~ 1.80</t>
         </is>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="H8" s="4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>29.94</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>1.59</t>
@@ -2097,8 +2117,12 @@
           <t>1.20 ~ 2.20</t>
         </is>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>30.94</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>1.66</t>
@@ -2327,8 +2351,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="H10" s="4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>48.94</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>1.73</t>
@@ -2557,8 +2585,12 @@
           <t>1.50 ~ 1.90</t>
         </is>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="H11" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>44.94</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -3009,8 +3041,12 @@
           <t>1.20 ~ 2.20</t>
         </is>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="H13" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>42.94</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>1.69</t>
@@ -3066,7 +3102,9 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U13" s="3"/>
+      <c r="U13" s="4" t="n">
+        <v>4.32</v>
+      </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
@@ -3233,8 +3271,12 @@
           <t>1.50 ~ 2.30</t>
         </is>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="H14" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>52.94</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>1.77</t>
@@ -3697,8 +3739,12 @@
           <t>1.40 ~ 2.40</t>
         </is>
       </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="H16" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>26.74</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>1.68</t>
@@ -3925,8 +3971,12 @@
           <t>2.00 ~ 2.18</t>
         </is>
       </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="H17" s="4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>50.03</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -4149,8 +4199,12 @@
           <t>1.50 ~ 1.78</t>
         </is>
       </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="H18" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>53.43</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
           <t>1.75</t>
@@ -5061,8 +5115,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="H22" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>38.74</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -5106,7 +5164,9 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U22" s="3"/>
+      <c r="U22" s="4" t="n">
+        <v>3.88</v>
+      </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
@@ -5273,8 +5333,12 @@
           <t>1.70 ~ 2.30</t>
         </is>
       </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="H23" s="4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>53.74</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t>2.00</t>
@@ -6185,8 +6249,12 @@
           <t>1.60 ~ 2.60</t>
         </is>
       </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="H27" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>58.74</v>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
           <t>2.03</t>
@@ -7324,15 +7392,19 @@
         <v>10.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
           <t>1.70 ~ 2.60</t>
         </is>
       </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="H32" s="4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>39.03</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
           <t>1.95</t>
@@ -8200,55 +8272,53 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26西部证券CP008</t>
+          <t>26济产01(取消发行)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>09-10 17:00</t>
+          <t>09-10 19:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>072610179.IB</t>
+          <t>DY283929.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>0.48Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>30.29</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26西部证券CP005</t>
+          <t>26济南产业PPN002A</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>158D</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.5147</t>
+          <t>1.9623</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -8258,12 +8328,12 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>西部证券股份有限公司</t>
+          <t>济南产业发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B- 37.42</t>
+          <t>C 26.50</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8273,7 +8343,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8283,19 +8353,19 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.55%~1.59%</t>
+          <t>1.89%~1.99%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8306,19 +8376,23 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
-        </is>
-      </c>
-      <c r="AB36" s="3"/>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金7亿元拟用于偿还公司债券本金[24济产01]</t>
+        </is>
+      </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>西部证券股份有限公司</t>
+          <t>中银国际证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8328,68 +8402,68 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>西部证券股份有限公司2026年度第八期短期融资券</t>
+          <t>济南产业发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AM36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8422,49 +8496,55 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26厦门银行二级资本债券01</t>
+          <t>26西部证券CP008</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>09-10 00:00</t>
-        </is>
-      </c>
-      <c r="C37" s="3"/>
+          <t>09-10 17:00</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>072610179.IB</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>0.48Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>1.60 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+        <v>15.0</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="G37" s="3"/>
+      <c r="H37" s="4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>30.29</v>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>21厦门银行二级02(柜台)</t>
+          <t>26西部证券CP005</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>77D+5.00Y</t>
+          <t>158D</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.5135</t>
+          <t>1.5147</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8474,12 +8554,12 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>厦门银行股份有限公司</t>
+          <t>西部证券股份有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>A- 60.10</t>
+          <t>B- 37.42</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8489,7 +8569,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-10 00:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8499,19 +8579,19 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.55%~1.59%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8519,35 +8599,27 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z37" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+      <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
-        </is>
-      </c>
-      <c r="AB37" s="3" t="inlineStr">
-        <is>
-          <t>本期债券募集资金将依据适用法律和监管部门的批准用于补充发行人二级资本</t>
-        </is>
-      </c>
+          <t>陕西省-西安市</t>
+        </is>
+      </c>
+      <c r="AB37" s="3"/>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,中信建投证券股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,财达证券股份有限公司</t>
+          <t>西部证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8557,7 +8629,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>厦门银行股份有限公司2026年二级资本债券(第一期)</t>
+          <t>西部证券股份有限公司2026年度第八期短期融资券</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8567,64 +8639,60 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2036-09-14</t>
-        </is>
-      </c>
-      <c r="AK37" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-03-05</t>
+        </is>
+      </c>
+      <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO37" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ37" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR37" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>城商行</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
       <c r="AV37" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8632,12 +8700,12 @@
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY37" s="3" t="inlineStr">
@@ -8650,49 +8718,49 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26农业银行绿色债02</t>
+          <t>26厦门银行二级资本债券01</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-10 00:00</t>
         </is>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26农业银行绿色债01(柜台)</t>
+          <t>21厦门银行二级02(柜台)</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>77D+5.00Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.5314</t>
+          <t>1.5135</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -8702,12 +8770,12 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司</t>
+          <t>厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>S 90.45</t>
+          <t>A- 60.10</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8717,7 +8785,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 00:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8734,12 +8802,12 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -8749,33 +8817,33 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。</t>
+          <t>本期债券募集资金将依据适用法律和监管部门的批准用于补充发行人二级资本</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,中银国际证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,招商证券股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,广发证券股份有限公司</t>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,中信建投证券股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,财达证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
@@ -8785,7 +8853,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司2026年绿色金融债券(第二期)(债券通)</t>
+          <t>厦门银行股份有限公司2026年二级资本债券(第一期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8795,10 +8863,14 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
-        </is>
-      </c>
-      <c r="AK38" s="3"/>
+          <t>2036-09-14</t>
+        </is>
+      </c>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8821,7 +8893,7 @@
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
@@ -8836,7 +8908,7 @@
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>国有银行</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
@@ -8846,7 +8918,7 @@
       </c>
       <c r="AU38" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-14</t>
         </is>
       </c>
       <c r="AV38" s="3" t="inlineStr">
@@ -8856,12 +8928,12 @@
       </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX38" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AY38" s="3" t="inlineStr">
@@ -8874,7 +8946,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26水电七局MTN002</t>
+          <t>26农业银行绿色债02</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8882,47 +8954,45 @@
           <t>09-10 18:00</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>102683579.IB</t>
-        </is>
-      </c>
+      <c r="C39" s="3"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>30.0</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+          <t>1.30 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>32.94</v>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26水电七局MTN001(科创债)</t>
+          <t>26农业银行绿色债01(柜台)</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>2.61Y+N</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.7692</t>
+          <t>1.5314</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -8932,12 +9002,12 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>中国水利水电第七工程局有限公司</t>
+          <t>中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.17</t>
+          <t>S 90.45</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8957,55 +9027,55 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="U39" s="4" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>1.28</v>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z39" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据注册20亿元,本期发行金额5亿元,拟用于偿还发行人有息债务[23水电七局MTN002]</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,中银国际证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,招商证券股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr">
@@ -9015,7 +9085,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>中国水利水电第七工程局有限公司2026年度第二期中期票据</t>
+          <t>中国农业银行股份有限公司2026年绿色金融债券(第二期)(债券通)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9025,53 +9095,53 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>其他专业工程</t>
+          <t>国有银行</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9086,12 +9156,12 @@
       </c>
       <c r="AW39" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX39" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY39" s="3" t="inlineStr">
@@ -9104,7 +9174,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26陕西金融MTN003</t>
+          <t>26水电七局MTN002</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9114,12 +9184,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>102683588.IB</t>
+          <t>102683579.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -9130,29 +9200,33 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>52.94</v>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26陕西金融MTN002</t>
+          <t>26水电七局MTN001(科创债)</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>2.61Y+N</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2.0147</t>
+          <t>1.7692</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -9162,12 +9236,12 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>陕西金融资产管理股份有限公司</t>
+          <t>中国水利水电第七工程局有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 16.28</t>
+          <t>D+ 9.17</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9191,40 +9265,40 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>4.34</v>
+        <v>3.96</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额5亿元拟全部用于偿还发行人到期债务融资工具本金[23陕西金融MTN003]</t>
+          <t>发行人本期中期票据注册20亿元,本期发行金额5亿元,拟用于偿还发行人有息债务[23水电七局MTN002]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>交通银行股份有限公司,华夏银行股份有限公司</t>
+          <t>招商银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -9235,7 +9309,7 @@
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
@@ -9245,7 +9319,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>陕西金融资产管理股份有限公司2026年度第三期中期票据</t>
+          <t>中国水利水电第七工程局有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9255,7 +9329,7 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
@@ -9266,7 +9340,7 @@
       </c>
       <c r="AM40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN40" s="3" t="inlineStr">
@@ -9276,32 +9350,32 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>其他专业工程</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9316,12 +9390,12 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY40" s="3" t="inlineStr">
@@ -9334,7 +9408,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26中铁十局MTN001</t>
+          <t>26陕西金融MTN003</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9344,45 +9418,49 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>102683587.IB</t>
+          <t>102683588.IB</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+          <t>1.70 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>42.74</v>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>25中铁十局MTN001</t>
+          <t>26陕西金融MTN002</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>4.12Y+N</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>2.0901</t>
+          <t>2.0147</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -9392,12 +9470,12 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>中铁十局集团有限公司</t>
+          <t>陕西金融资产管理股份有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 16.28</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9407,7 +9485,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9421,15 +9499,19 @@
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>3.3</v>
+        <v>4.34</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W41" s="3"/>
+        <v>1.4</v>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -9437,24 +9519,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据采取发行金额动态调整机制,基础发行规模人民币0亿元,发行金额上限14亿元,拟用于偿还发行人有息债务。</t>
+          <t>发行人本期中期票据发行金额5亿元拟全部用于偿还发行人到期债务融资工具本金[23陕西金融MTN003]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>交通银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9465,7 +9543,7 @@
       </c>
       <c r="AF41" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG41" s="3" t="inlineStr">
@@ -9475,7 +9553,7 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>中铁十局集团有限公司2026年度第一期中期票据</t>
+          <t>陕西金融资产管理股份有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9506,32 +9584,32 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>其他专业工程</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9546,12 +9624,12 @@
       </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX41" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY41" s="3" t="inlineStr">
@@ -9564,7 +9642,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26首钢SCP006</t>
+          <t>26中铁十局MTN001</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9574,60 +9652,64 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>012682230.IB</t>
+          <t>102683587.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>0.71Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 1.52</t>
-        </is>
-      </c>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>61.74</v>
+      </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26首钢SCP005</t>
+          <t>25中铁十局MTN001</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>231D</t>
+          <t>4.12Y+N</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.5093</t>
+          <t>2.0901</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/1.5150</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>首钢集团有限公司</t>
+          <t>中铁十局集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>B- 37.97</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9637,7 +9719,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9651,19 +9733,15 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>1.13</v>
+        <v>3.3</v>
       </c>
       <c r="V42" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+        <v>1.19</v>
+      </c>
+      <c r="W42" s="3"/>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -9671,31 +9749,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z42" s="3"/>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具募集资金15亿元,拟用于偿还有息债务。</t>
+          <t>本期中期票据采取发行金额动态调整机制,基础发行规模人民币0亿元,发行金额上限14亿元,拟用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG42" s="3" t="inlineStr">
@@ -9705,7 +9787,7 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>首钢集团有限公司2026年度第六期超短期融资券</t>
+          <t>中铁十局集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9715,7 +9797,7 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
@@ -9741,27 +9823,27 @@
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>其他专业工程</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
@@ -9776,12 +9858,12 @@
       </c>
       <c r="AW42" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX42" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY42" s="3" t="inlineStr">
@@ -9794,7 +9876,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26吉林高速MTN008</t>
+          <t>26首钢SCP006</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9804,60 +9886,64 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>102683585.IB</t>
+          <t>012682230.IB</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.71Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+          <t>1.25 ~ 1.52</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>14.43</v>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26吉林高速MTN007</t>
+          <t>26首钢SCP005</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+2.00Y</t>
+          <t>231D</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.7410</t>
+          <t>1.5093</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>1.7500/--</t>
+          <t>--/1.5150</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>吉林省高速公路集团有限公司</t>
+          <t>首钢集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>B 50.35</t>
+          <t>B- 37.97</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9867,7 +9953,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -9881,19 +9967,19 @@
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>4.32</v>
+        <v>1.13</v>
       </c>
       <c r="V43" s="4" t="n">
-        <v>1.46</v>
+        <v>1.0</v>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -9901,30 +9987,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z43" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>吉林省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元，发行金额上限为10亿元，拟全部用于偿还发行人有息债务本息。</t>
+          <t>本期债务融资工具募集资金15亿元,拟用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
+          <t>广发银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -9939,7 +10021,7 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>吉林省高速公路集团有限公司2026年度第八期中期票据</t>
+          <t>首钢集团有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -9949,7 +10031,7 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2027-05-28</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
@@ -9970,37 +10052,37 @@
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t/>
         </is>
       </c>
       <c r="AV43" s="3" t="inlineStr">
@@ -10010,7 +10092,7 @@
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
@@ -10028,7 +10110,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26华电新能MTN001</t>
+          <t>26吉林高速MTN008</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -10038,60 +10120,64 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>102683601.IB</t>
+          <t>102683585.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
+          <t>1.40 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>30.74</v>
+      </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>G26HX2</t>
+          <t>26吉林高速MTN007</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>4.79Y</t>
+          <t>2.96Y+2.00Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.7418</t>
+          <t>1.7410</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>华电新能源集团股份有限公司</t>
+          <t>吉林省高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>A- 63.03</t>
+          <t>B 50.35</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10101,7 +10187,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>09-10 10:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10114,16 +10200,20 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U44" s="3"/>
-      <c r="V44" s="3"/>
+      <c r="U44" s="4" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>1.46</v>
+      </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -10131,20 +10221,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z44" s="3"/>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>吉林省</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为15亿元,募集资金拟全部用于偿还发行人及发行人所属公司到期债务及补充流动资金。</t>
+          <t>本期中期票据基础发行规模为0亿元，发行金额上限为10亿元，拟全部用于偿还发行人有息债务本息。</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
@@ -10155,7 +10249,7 @@
       </c>
       <c r="AF44" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG44" s="3" t="inlineStr">
@@ -10165,7 +10259,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>华电新能源集团股份有限公司2026年度第一期中期票据</t>
+          <t>吉林省高速公路集团有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10196,37 +10290,37 @@
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AV44" s="3" t="inlineStr">
@@ -10236,7 +10330,7 @@
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
@@ -10254,7 +10348,7 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26首都机场SCP006</t>
+          <t>26华电新能MTN001</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10264,60 +10358,64 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>012682229.IB</t>
+          <t>102683601.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
-        </is>
-      </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
+          <t>1.40 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>27.74</v>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26首都机场SCP005</t>
+          <t>G26HX2</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>174D</t>
+          <t>4.79Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.4919</t>
+          <t>1.7418</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>1.5100/1.3796</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>首都机场集团有限公司</t>
+          <t>华电新能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C 28.71</t>
+          <t>A- 63.03</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10327,7 +10425,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 10:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10340,16 +10438,20 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U45" s="3"/>
-      <c r="V45" s="3"/>
+      <c r="U45" s="4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>1.05</v>
+      </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10360,28 +10462,28 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期发行10亿元超短期融资券，全部用于偿还发行人有息债务。</t>
+          <t>本期发行金额为15亿元,募集资金拟全部用于偿还发行人及发行人所属公司到期债务及补充流动资金。</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG45" s="3" t="inlineStr">
@@ -10391,7 +10493,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>首都机场集团有限公司2026年度第六期超短期融资券</t>
+          <t>华电新能源集团股份有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10401,7 +10503,7 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2027-03-10</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10427,27 +10529,27 @@
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>机场</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>机场</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>机场</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10480,7 +10582,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26长春城投MTN001</t>
+          <t>26首都机场SCP006</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10490,12 +10592,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>102683602.IB</t>
+          <t>012682229.IB</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
@@ -10506,44 +10608,48 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
+          <t>1.30 ~ 1.50</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>16.29</v>
+      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>25长春城投MTN001A</t>
+          <t>26首都机场SCP005</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>3.78Y+5.00Y</t>
+          <t>174D</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2.0296</t>
+          <t>1.4919</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/1.3796</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>长春城投建设投资(集团)有限公司</t>
+          <t>首都机场集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C- 12.72</t>
+          <t>C 28.71</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10553,7 +10659,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -10566,20 +10672,16 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U46" s="4" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>1.72</v>
-      </c>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>2.01%~2.11%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -10590,23 +10692,23 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>吉林省-长春市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期基础发行金额人民币0亿元,本期发行金额上限人民币10亿元(含10亿元),募集资金全部用于偿还发行人债务融资工具本金。[23长春城投MTN003]</t>
+          <t>本期发行10亿元超短期融资券，全部用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,浙商证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
@@ -10621,7 +10723,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>长春城投建设投资(集团)有限公司2026年度第一期中期票据</t>
+          <t>首都机场集团有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10631,7 +10733,7 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2027-03-10</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
@@ -10652,12 +10754,12 @@
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
@@ -10667,17 +10769,17 @@
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>机场</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>机场</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>机场</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10705,14 +10807,12 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ46" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ46" s="3"/>
     </row>
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26津渤海MTN013</t>
+          <t>26长春城投MTN001</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10722,60 +10822,64 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>102683603.IB</t>
+          <t>102683602.IB</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>62.94</v>
+      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26津渤海MTN012</t>
+          <t>25长春城投MTN001A</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>1.96Y</t>
+          <t>3.78Y+5.00Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>2.2654</t>
+          <t>2.0296</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>2.2400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>天津渤海国有资产经营管理有限公司</t>
+          <t>长春城投建设投资(集团)有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C 29.92</t>
+          <t>C- 12.72</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10785,7 +10889,7 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -10799,19 +10903,19 @@
         </is>
       </c>
       <c r="U47" s="4" t="n">
-        <v>4.3</v>
+        <v>4.93</v>
       </c>
       <c r="V47" s="4" t="n">
-        <v>1.31</v>
+        <v>1.72</v>
       </c>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>2.16%~2.26%</t>
+          <t>2.01%~2.11%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
@@ -10822,17 +10926,17 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>吉林省-长春市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据本期发行采用发行金额动态调整机制，基础发行金额0.00亿元，发行金额上限4.00亿元，拟用于偿还发行人本部到期债务融资工具本金。[24津渤海MTN008]</t>
+          <t>本期基础发行金额人民币0亿元,本期发行金额上限人民币10亿元(含10亿元),募集资金全部用于偿还发行人债务融资工具本金。[23长春城投MTN003]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,国投证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
@@ -10853,7 +10957,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>天津渤海国有资产经营管理有限公司2026年度第十三期中期票据</t>
+          <t>长春城投建设投资(集团)有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -10863,7 +10967,7 @@
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2028-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK47" s="3"/>
@@ -10884,32 +10988,32 @@
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -10938,13 +11042,13 @@
         </is>
       </c>
       <c r="AZ47" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26北京农商绿色债</t>
+          <t>26津渤海MTN013</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -10952,56 +11056,66 @@
           <t>09-10 18:00</t>
         </is>
       </c>
-      <c r="C48" s="3"/>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>102683603.IB</t>
+        </is>
+      </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="F48" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
+          <t>1.90 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>89.79</v>
+      </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>25北京农商科创债(柜台)</t>
+          <t>26津渤海MTN012</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>4.25Y</t>
+          <t>1.96Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.6323</t>
+          <t>2.2654</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.2400/--</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>北京农村商业银行股份有限公司</t>
+          <t>天津渤海国有资产经营管理有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>A 80.00</t>
+          <t>C 29.92</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11021,19 +11135,23 @@
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="U48" s="3"/>
-      <c r="V48" s="3"/>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>1.31</v>
+      </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>2.16%~2.26%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
@@ -11041,26 +11159,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z48" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="AB48" s="3"/>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>本期中期票据本期发行采用发行金额动态调整机制，基础发行金额0.00亿元，发行金额上限4.00亿元，拟用于偿还发行人本部到期债务融资工具本金。[24津渤海MTN008]</t>
+        </is>
+      </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,中国邮政储蓄银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中信银行股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
@@ -11075,7 +11193,7 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>北京农村商业银行股份有限公司2026年绿色金融债券</t>
+          <t>天津渤海国有资产经营管理有限公司2026年度第十三期中期票据</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
@@ -11085,60 +11203,60 @@
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t>2028-09-11</t>
         </is>
       </c>
       <c r="AK48" s="3"/>
       <c r="AL48" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO48" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ48" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR48" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>农商行</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV48" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -11159,12 +11277,14 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ48" s="3"/>
+      <c r="AZ48" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26绿城水务MTN003</t>
+          <t>26北京农商绿色债</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -11172,47 +11292,45 @@
           <t>09-10 18:00</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>102683591.IB</t>
-        </is>
-      </c>
+      <c r="C49" s="3"/>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>30.0</v>
+      </c>
+      <c r="F49" s="3"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>1.65 ~ 2.05</t>
-        </is>
-      </c>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
+          <t>1.30 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>30.94</v>
+      </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>26绿城水务MTN002</t>
+          <t>25北京农商科创债(柜台)</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>4.68Y</t>
+          <t>4.25Y</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>2.0101</t>
+          <t>1.6323</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -11222,12 +11340,12 @@
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>广西绿城水务集团股份有限公司</t>
+          <t>北京农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.49</t>
+          <t>A 80.00</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -11237,7 +11355,7 @@
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
@@ -11247,50 +11365,48 @@
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U49" s="4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="V49" s="4" t="n">
-        <v>3.13</v>
-      </c>
+        <v>3.55</v>
+      </c>
+      <c r="V49" s="3"/>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X49" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y49" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z49" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
-        </is>
-      </c>
-      <c r="AB49" s="3" t="inlineStr">
-        <is>
-          <t>发行人拟发行金额为5亿元，募集资金中，4亿元用于偿还发行人本部债务融资工具本金，1亿元用于偿还发行人有息债务。[23绿城水务MTN003 ]</t>
-        </is>
-      </c>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AB49" s="3"/>
       <c r="AC49" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,兴业银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国工商银行股份有限公司,中国农业银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司,中国邮政储蓄银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD49" s="3"/>
       <c r="AE49" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF49" s="3" t="inlineStr">
@@ -11305,7 +11421,7 @@
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>广西绿城水务集团股份有限公司2026年度第三期中期票据</t>
+          <t>北京农村商业银行股份有限公司2026年绿色金融债券</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
@@ -11315,53 +11431,53 @@
       </c>
       <c r="AJ49" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AK49" s="3"/>
       <c r="AL49" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AM49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP49" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ49" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT49" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU49" s="3" t="inlineStr">
@@ -11389,81 +11505,79 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ49" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ49" s="3"/>
     </row>
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>26江南农商行债01</t>
+          <t>26绿城水务MTN003</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>09-10 16:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>212680039.IB</t>
+          <t>102683591.IB</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.65 ~ 2.05</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>33.94</v>
+        <v>45.74</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>24江南农商行债01</t>
+          <t>26绿城水务MTN002</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>1.02Y</t>
+          <t>4.68Y</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1.4956</t>
+          <t>2.0101</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>1.5200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>江苏江南农村商业银行股份有限公司</t>
+          <t>广西绿城水务集团股份有限公司</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>B- 40.72</t>
+          <t>D+ 5.49</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11473,7 +11587,7 @@
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -11483,51 +11597,55 @@
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="U50" s="3"/>
-      <c r="V50" s="3"/>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U50" s="4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>3.13</v>
+      </c>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z50" s="3"/>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">本期债券募集的资金将用于优化中长期资产负债匹配结构，增加稳定中长期负债来源并支持中长期资产业务的开展。 </t>
+          <t>发行人拟发行金额为5亿元，募集资金中，4亿元用于偿还发行人本部债务融资工具本金，1亿元用于偿还发行人有息债务。[23绿城水务MTN003 ]</t>
         </is>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,中国邮政储蓄银行股份有限公司,国信证券股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,兴业银行股份有限公司,光大证券股份有限公司,招商证券股份有限公司,华夏银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD50" s="3"/>
       <c r="AE50" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF50" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG50" s="3" t="inlineStr">
@@ -11537,7 +11655,7 @@
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>江苏江南农村商业银行股份有限公司2026年金融债券(第一期)</t>
+          <t>广西绿城水务集团股份有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
@@ -11547,60 +11665,60 @@
       </c>
       <c r="AJ50" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK50" s="3"/>
       <c r="AL50" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO50" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ50" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR50" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS50" s="3" t="inlineStr">
-        <is>
-          <t>农商行</t>
-        </is>
-      </c>
-      <c r="AT50" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU50" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV50" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -11621,20 +11739,26 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ50" s="3"/>
+      <c r="AZ50" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26中银金租债03BC</t>
+          <t>26江南农商行债01</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
-        </is>
-      </c>
-      <c r="C51" s="3"/>
+          <t>09-10 16:00</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>212680039.IB</t>
+        </is>
+      </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -11643,47 +11767,53 @@
       <c r="E51" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F51" s="3"/>
+      <c r="F51" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
+          <t>1.30 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>33.94</v>
+      </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>26中银金租债02BC</t>
+          <t>24江南农商行债01</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>2.75Y</t>
+          <t>1.02Y</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1.6697</t>
+          <t>1.4956</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>1.6900/1.6600</t>
+          <t>1.5200/--</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>中银金融租赁有限公司</t>
+          <t>江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>B- 40.72</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -11710,12 +11840,12 @@
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X51" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y51" s="3" t="inlineStr">
@@ -11723,35 +11853,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z51" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z51" s="3"/>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据国家法律法规及政策要求,主要用于补充公司中长期资金来源,优化公司资产负债期限结构,部分用于海洋经济相关租赁项目的新增投放或存量融资置换</t>
+          <t xml:space="preserve">本期债券募集的资金将用于优化中长期资产负债匹配结构，增加稳定中长期负债来源并支持中长期资产业务的开展。 </t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中信证券股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司,中国农业银行股份有限公司,中国邮政储蓄银行股份有限公司,兴业银行股份有限公司,北京银行股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,中国邮政储蓄银行股份有限公司,国信证券股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,兴业银行股份有限公司,光大证券股份有限公司,招商证券股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD51" s="3"/>
       <c r="AE51" s="3" t="inlineStr">
         <is>
-          <t>其他金融债</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF51" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG51" s="3" t="inlineStr">
@@ -11761,7 +11887,7 @@
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>中银金融租赁有限公司2026年金融债券(第三期)(债券通)</t>
+          <t>江苏江南农村商业银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
@@ -11797,27 +11923,27 @@
       </c>
       <c r="AP51" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ51" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>金融租赁</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
         <is>
-          <t>金融租赁</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT51" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU51" s="3" t="inlineStr">
@@ -11850,7 +11976,7 @@
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26连云工投CP002</t>
+          <t>26中银金租债03BC</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -11858,62 +11984,56 @@
           <t>09-10 18:00</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>042680312.IB</t>
-        </is>
-      </c>
+      <c r="C52" s="3"/>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>0.99Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>26连云工投CP001</t>
+          <t>26中银金租债02BC</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>320D</t>
+          <t>2.75Y</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1.6553</t>
+          <t>1.6697</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/1.6600</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>连云港市工业投资集团有限公司</t>
+          <t>中银金融租赁有限公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.44</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -11933,55 +12053,55 @@
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="U52" s="4" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>8.0</v>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.69%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z52" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>本期发行规模5.00亿元，用于偿还有息债务[26连云工投SCP002]</t>
+          <t>本期债券募集资金将依据国家法律法规及政策要求,主要用于补充公司中长期资金来源,优化公司资产负债期限结构,部分用于海洋经济相关租赁项目的新增投放或存量融资置换</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,交通银行股份有限公司</t>
+          <t>中国银行股份有限公司,中信证券股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司,中国农业银行股份有限公司,中国邮政储蓄银行股份有限公司,兴业银行股份有限公司,北京银行股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
       <c r="AE52" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>其他金融债</t>
         </is>
       </c>
       <c r="AF52" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG52" s="3" t="inlineStr">
@@ -11991,7 +12111,7 @@
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>连云港市工业投资集团有限公司2026年度第二期短期融资券</t>
+          <t>中银金融租赁有限公司2026年金融债券(第三期)(债券通)</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
@@ -12001,53 +12121,53 @@
       </c>
       <c r="AJ52" s="3" t="inlineStr">
         <is>
-          <t>2027-09-06</t>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AK52" s="3"/>
       <c r="AL52" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AM52" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP52" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ52" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>金融租赁</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>金融租赁</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>化学原料</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -12075,14 +12195,12 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ52" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ52" s="3"/>
     </row>
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26海江投资MTN003</t>
+          <t>26连云工投CP002</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -12092,45 +12210,49 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>102683596.IB</t>
+          <t>042680312.IB</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.99Y</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>5.5</v>
+        <v>5.0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>5.5</v>
+        <v>5.0</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>34.98</v>
+      </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>26海江投资MTN002</t>
+          <t>26连云工投CP001</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>2.60Y+2.00Y</t>
+          <t>320D</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1.6979</t>
+          <t>1.6553</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -12140,12 +12262,12 @@
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>宁波市镇海区海江投资发展有限公司</t>
+          <t>连云港市工业投资集团有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>C- 18.80</t>
+          <t>D+ 8.44</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12169,19 +12291,19 @@
         </is>
       </c>
       <c r="U53" s="4" t="n">
-        <v>5.13</v>
+        <v>3.08</v>
       </c>
       <c r="V53" s="4" t="n">
-        <v>1.07</v>
+        <v>8.0</v>
       </c>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.65%~1.69%</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
@@ -12192,23 +12314,23 @@
       <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期发行5.5亿元中期票据,募集资金全部用于偿还发行人的债务融资工具的本金[21海江投资MTN002]</t>
+          <t>本期发行规模5.00亿元，用于偿还有息债务[26连云工投SCP002]</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,交通银行股份有限公司</t>
+          <t>南京银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD53" s="3"/>
       <c r="AE53" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF53" s="3" t="inlineStr">
@@ -12223,7 +12345,7 @@
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>宁波市镇海区海江投资发展有限公司2026年度第三期中期票据</t>
+          <t>连云港市工业投资集团有限公司2026年度第二期短期融资券</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
@@ -12233,7 +12355,7 @@
       </c>
       <c r="AJ53" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2027-09-06</t>
         </is>
       </c>
       <c r="AK53" s="3"/>
@@ -12254,37 +12376,37 @@
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP53" s="3" t="inlineStr">
         <is>
-          <t>7*无效</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ53" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AT53" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>化学原料</t>
         </is>
       </c>
       <c r="AU53" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t/>
         </is>
       </c>
       <c r="AV53" s="3" t="inlineStr">
@@ -12294,7 +12416,7 @@
       </c>
       <c r="AW53" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX53" s="3" t="inlineStr">
@@ -12307,12 +12429,14 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ53" s="3"/>
+      <c r="AZ53" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26靖江滨江MTN001</t>
+          <t>26海江投资MTN003</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -12322,45 +12446,49 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>102683581.IB</t>
+          <t>102683596.IB</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2.0</v>
+        <v>5.5</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2.0</v>
+        <v>5.5</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
+          <t>1.60 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>27.74</v>
+      </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>24靖江滨江MTN003</t>
+          <t>26海江投资MTN002</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>1.26Y</t>
+          <t>2.60Y+2.00Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.6053</t>
+          <t>1.6979</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -12370,12 +12498,12 @@
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司</t>
+          <t>宁波市镇海区海江投资发展有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C 28.44</t>
+          <t>C- 18.80</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12399,40 +12527,40 @@
         </is>
       </c>
       <c r="U54" s="4" t="n">
-        <v>3.05</v>
+        <v>5.13</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>1.0</v>
+        <v>1.07</v>
       </c>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额2亿元,募集资金拟用于偿还发行人有息债务[25靖江滨江PPN002]</t>
+          <t>本期发行5.5亿元中期票据,募集资金全部用于偿还发行人的债务融资工具的本金[21海江投资MTN002]</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>宁波银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD54" s="3"/>
@@ -12453,7 +12581,7 @@
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司2026年度第一期中期票据</t>
+          <t>宁波市镇海区海江投资发展有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
@@ -12463,7 +12591,7 @@
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>2028-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK54" s="3"/>
@@ -12484,27 +12612,27 @@
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP54" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7*无效</t>
         </is>
       </c>
       <c r="AQ54" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT54" s="3" t="inlineStr">
@@ -12514,7 +12642,7 @@
       </c>
       <c r="AU54" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AV54" s="3" t="inlineStr">
@@ -12524,7 +12652,7 @@
       </c>
       <c r="AW54" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX54" s="3" t="inlineStr">
@@ -12537,14 +12665,12 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ54" s="4" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="AZ54" s="3"/>
     </row>
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26张家城投MTN006</t>
+          <t>26靖江滨江MTN001</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -12554,60 +12680,64 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>102683595.IB</t>
+          <t>102683581.IB</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1.6</v>
+        <v>2.0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1.6</v>
+        <v>2.0</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>44.79</v>
+      </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>26张家城投MTN004</t>
+          <t>24靖江滨江MTN003</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>6.82Y</t>
+          <t>1.26Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>2.0558</t>
+          <t>1.6053</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>2.0800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>张家港市城市投资发展集团有限公司</t>
+          <t>靖江市滨江新城投资开发有限公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>C 25.21</t>
+          <t>C 28.44</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -12631,40 +12761,40 @@
         </is>
       </c>
       <c r="U55" s="4" t="n">
-        <v>2.13</v>
+        <v>3.05</v>
       </c>
       <c r="V55" s="4" t="n">
-        <v>2.67</v>
+        <v>1.0</v>
       </c>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X55" s="3" t="inlineStr">
         <is>
-          <t>1.93%~2.03%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额1.6亿元,拟全部用于偿还本部债务融资工具本金。[26张家城投SCP001,21张家城投MTN004]</t>
+          <t>本次中期票据发行金额2亿元,募集资金拟用于偿还发行人有息债务[25靖江滨江PPN002]</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD55" s="3"/>
@@ -12685,7 +12815,7 @@
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>张家港市城市投资发展集团有限公司2026年度第六期中期票据</t>
+          <t>靖江市滨江新城投资开发有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
@@ -12695,14 +12825,10 @@
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
-          <t>2033-09-11</t>
-        </is>
-      </c>
-      <c r="AK55" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-09-11</t>
+        </is>
+      </c>
+      <c r="AK55" s="3"/>
       <c r="AL55" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
@@ -12720,32 +12846,32 @@
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP55" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ55" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT55" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU55" s="3" t="inlineStr">
@@ -12773,12 +12899,14 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ55" s="3"/>
+      <c r="AZ55" s="4" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26苏州港MTN003(并购)</t>
+          <t>26张家城投MTN006</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -12788,60 +12916,64 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>102683599.IB</t>
+          <t>102683595.IB</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
+          <t>1.90 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>55.44</v>
+      </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>26苏州港MTN001</t>
+          <t>26张家城投MTN004</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2.68Y</t>
+          <t>6.82Y</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.7252</t>
+          <t>2.0558</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>1.7500/--</t>
+          <t>2.0800/--</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>江苏苏州港集团有限公司</t>
+          <t>张家港市城市投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>C- 16.12</t>
+          <t>C 25.21</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -12864,21 +12996,25 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
+      <c r="U56" s="4" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>2.67</v>
+      </c>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.93%~2.03%</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z56" s="3"/>
@@ -12889,12 +13025,12 @@
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据本期发行金额1.5亿元,其中0.72亿元用于偿还发行人本部及下属子公司的有息负债,0.78亿元用于并购用途,支付对子公司太仓鑫海港口开发有限公司增资款项。</t>
+          <t>本期发行金额1.6亿元,拟全部用于偿还本部债务融资工具本金。[26张家城投SCP001,21张家城投MTN004]</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD56" s="3"/>
@@ -12915,7 +13051,7 @@
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>江苏苏州港集团有限公司2026年度第三期中期票据(并购)</t>
+          <t>张家港市城市投资发展集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
@@ -12925,10 +13061,14 @@
       </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
-        </is>
-      </c>
-      <c r="AK56" s="3"/>
+          <t>2033-09-11</t>
+        </is>
+      </c>
+      <c r="AK56" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL56" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
@@ -12946,32 +13086,32 @@
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP56" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ56" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT56" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU56" s="3" t="inlineStr">
@@ -13004,7 +13144,7 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26深圳国际MTN004A</t>
+          <t>26苏州港MTN003(并购)</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -13014,60 +13154,64 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>102683582.IB</t>
+          <t>102683599.IB</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>5.0</v>
+        <v>1.5</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>5.0</v>
+        <v>1.5</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
+          <t>1.50 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>46.94</v>
+      </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>26深圳国控MTN003</t>
+          <t>26苏州港MTN001</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>4.85Y</t>
+          <t>2.68Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>1.7449</t>
+          <t>1.7252</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>--/1.7450</t>
+          <t>1.7500/--</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>深圳国际控股有限公司</t>
+          <t>江苏苏州港集团有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>B- 35.42</t>
+          <t>C- 16.12</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13077,7 +13221,7 @@
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>09-10 14:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -13090,12 +13234,18 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U57" s="3"/>
+      <c r="U57" s="4" t="n">
+        <v>2.93</v>
+      </c>
       <c r="V57" s="3"/>
-      <c r="W57" s="3"/>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
       <c r="X57" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
@@ -13104,15 +13254,19 @@
         </is>
       </c>
       <c r="Z57" s="3"/>
-      <c r="AA57" s="3"/>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>江苏省-苏州市</t>
+        </is>
+      </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期中票发行规模上限为人民币10亿元,拟全部用于偿还发行人即将到期的境内有息债务本息[23国际P7]</t>
+          <t>本次中期票据本期发行金额1.5亿元,其中0.72亿元用于偿还发行人本部及下属子公司的有息负债,0.78亿元用于并购用途,支付对子公司太仓鑫海港口开发有限公司增资款项。</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,平安银行股份有限公司</t>
+          <t>招商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3"/>
@@ -13133,7 +13287,7 @@
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>深圳国际控股有限公司2026年度第四期中期票据(品种一)</t>
+          <t>江苏苏州港集团有限公司2026年度第三期中期票据(并购)</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
@@ -13143,7 +13297,7 @@
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK57" s="3"/>
@@ -13169,7 +13323,7 @@
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
@@ -13179,17 +13333,17 @@
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
@@ -13222,7 +13376,7 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26华能SCP012</t>
+          <t>26深圳国际MTN004A</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -13232,60 +13386,60 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>012682231.IB</t>
+          <t>102683582.IB</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>0.19Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>25.0</v>
+        <v>5.0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>25.0</v>
+        <v>5.0</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.46</t>
+          <t>1.30 ~ 2.20</t>
         </is>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>26华能SCP010</t>
+          <t>26深圳国控MTN003</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>41D</t>
+          <t>4.85Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.4639</t>
+          <t>1.7449</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>1.4750/1.4600</t>
+          <t>--/1.7450</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>华能国际电力股份有限公司</t>
+          <t>深圳国际控股有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>B- 45.00</t>
+          <t>B- 35.42</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13310,14 +13464,10 @@
       </c>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
-      <c r="W58" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="W58" s="3"/>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
@@ -13326,26 +13476,26 @@
         </is>
       </c>
       <c r="Z58" s="3"/>
-      <c r="AA58" s="3" t="inlineStr">
-        <is>
-          <t>河北省-保定市</t>
-        </is>
-      </c>
-      <c r="AB58" s="3"/>
+      <c r="AA58" s="3"/>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>本期中票发行规模上限为人民币10亿元,拟全部用于偿还发行人即将到期的境内有息债务本息[23国际P7]</t>
+        </is>
+      </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,北京银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
       <c r="AE58" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF58" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG58" s="3" t="inlineStr">
@@ -13355,7 +13505,7 @@
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>华能国际电力股份有限公司2026年度第十二期超短期融资券</t>
+          <t>深圳国际控股有限公司2026年度第四期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
@@ -13365,7 +13515,7 @@
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK58" s="3"/>
@@ -13391,27 +13541,27 @@
       </c>
       <c r="AP58" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ58" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU58" s="3" t="inlineStr">
@@ -13444,7 +13594,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26云能MTN005</t>
+          <t>26华能SCP012</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13454,60 +13604,64 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>102683589.IB</t>
+          <t>012682231.IB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.19Y</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
+          <t>1.26 ~ 1.46</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>14.18</v>
+      </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26云能MTN004</t>
+          <t>26华能SCP010</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>4.86Y</t>
+          <t>41D</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>2.0841</t>
+          <t>1.4639</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4750/1.4600</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司</t>
+          <t>华能国际电力股份有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.23</t>
+          <t>B- 45.00</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13517,7 +13671,7 @@
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>09-10 09:00</t>
+          <t>09-10 14:00</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
@@ -13530,20 +13684,16 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U59" s="4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V59" s="4" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="U59" s="3"/>
+      <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.99%~2.09%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
@@ -13554,28 +13704,24 @@
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>云南省</t>
-        </is>
-      </c>
-      <c r="AB59" s="3" t="inlineStr">
-        <is>
-          <t>本期中期票据发行规模10亿元，公司拟将募集资金扣除发行费用后全部用于偿还有息债务[24云能投MTN011]</t>
-        </is>
-      </c>
+          <t>河北省-保定市</t>
+        </is>
+      </c>
+      <c r="AB59" s="3"/>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
       <c r="AE59" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF59" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG59" s="3" t="inlineStr">
@@ -13585,7 +13731,7 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>云南省能源集团有限公司2026年度第五期中期票据</t>
+          <t>华能国际电力股份有限公司2026年度第十二期超短期融资券</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -13595,7 +13741,7 @@
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="AK59" s="3"/>
@@ -13621,27 +13767,27 @@
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -13669,14 +13815,12 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AZ59" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ59" s="3"/>
     </row>
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26太仓水务MTN003</t>
+          <t>26云能MTN005</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -13686,60 +13830,64 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>102683598.IB</t>
+          <t>102683589.IB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
+          <t>1.60 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>52.74</v>
+      </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>24太仓水务MTN002</t>
+          <t>26云能MTN004</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>4.86Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1.7376</t>
+          <t>2.0841</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>1.7600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>太仓市水务集团有限公司</t>
+          <t>云南省能源集团有限公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>C- 12.09</t>
+          <t>C+ 33.23</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -13763,10 +13911,10 @@
         </is>
       </c>
       <c r="U60" s="4" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="V60" s="4" t="n">
-        <v>13.0</v>
+        <v>1.3</v>
       </c>
       <c r="W60" s="3" t="inlineStr">
         <is>
@@ -13775,28 +13923,28 @@
       </c>
       <c r="X60" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.99%~2.09%</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金2亿元，发行人计划将募集资金全部用于偿还到期的有息负债。</t>
+          <t>本期中期票据发行规模10亿元，公司拟将募集资金扣除发行费用后全部用于偿还有息债务[24云能投MTN011]</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD60" s="3"/>
@@ -13817,7 +13965,7 @@
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>太仓市水务集团有限公司2026年度第三期中期票据</t>
+          <t>云南省能源集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
@@ -13827,7 +13975,7 @@
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK60" s="3"/>
@@ -13848,27 +13996,27 @@
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP60" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ60" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
@@ -13888,7 +14036,7 @@
       </c>
       <c r="AW60" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX60" s="3" t="inlineStr">
@@ -13902,7 +14050,7 @@
         </is>
       </c>
       <c r="AZ60" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="61" customHeight="true" ht="18.0">
@@ -14151,8 +14299,12 @@
           <t>1.70 ~ 2.70</t>
         </is>
       </c>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
+      <c r="H62" s="4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>92.74</v>
+      </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
           <t>2.54</t>
@@ -14607,8 +14759,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
+      <c r="H64" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>56.94</v>
+      </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
           <t>1.82</t>
@@ -14833,8 +14989,12 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
+      <c r="H65" s="4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>50.03</v>
+      </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
           <t>2.18</t>
@@ -15059,8 +15219,12 @@
           <t>1.40 ~ 2.40</t>
         </is>
       </c>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
+      <c r="H66" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>56.94</v>
+      </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
           <t>1.63</t>
@@ -15289,8 +15453,12 @@
           <t>1.30 ~ 1.70</t>
         </is>
       </c>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
+      <c r="H67" s="4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>26.18</v>
+      </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
           <t>1.58</t>
@@ -15578,7 +15746,9 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U68" s="3"/>
+      <c r="U68" s="4" t="n">
+        <v>3.59</v>
+      </c>
       <c r="V68" s="3"/>
       <c r="W68" s="3" t="inlineStr">
         <is>
@@ -15977,8 +16147,12 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
+      <c r="H70" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>83.74</v>
+      </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -16714,7 +16888,9 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U73" s="3"/>
+      <c r="U73" s="4" t="n">
+        <v>4.12</v>
+      </c>
       <c r="V73" s="3"/>
       <c r="W73" s="3" t="inlineStr">
         <is>
@@ -17634,7 +17810,9 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U77" s="3"/>
+      <c r="U77" s="4" t="n">
+        <v>1.41</v>
+      </c>
       <c r="V77" s="3"/>
       <c r="W77" s="3" t="inlineStr">
         <is>
@@ -18006,7 +18184,7 @@
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>26济产01</t>
+          <t>26济产02</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -18016,12 +18194,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>283929.SH</t>
+          <t>283930.SH</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
@@ -18030,34 +18208,38 @@
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
+          <t>1.80 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>78.74</v>
+      </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>26济南产业PPN002A</t>
+          <t>26济南产业PPN002B</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>1.9623</t>
+          <t>2.2911</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>1.9900/1.8500</t>
+          <t>2.3000/--</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
@@ -18099,7 +18281,7 @@
       </c>
       <c r="X79" s="3" t="inlineStr">
         <is>
-          <t>1.89%~1.99%</t>
+          <t>2.08%~2.18%</t>
         </is>
       </c>
       <c r="Y79" s="3" t="inlineStr">
@@ -18141,7 +18323,7 @@
       </c>
       <c r="AH79" s="3" t="inlineStr">
         <is>
-          <t>济南产业发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>济南产业发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI79" s="3" t="inlineStr">
@@ -18151,10 +18333,14 @@
       </c>
       <c r="AJ79" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
-        </is>
-      </c>
-      <c r="AK79" s="3"/>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK79" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL79" s="3" t="inlineStr">
         <is>
           <t/>
@@ -18230,7 +18416,7 @@
     <row r="80" customHeight="true" ht="18.0">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>26济产02</t>
+          <t>26川高K4</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -18240,7 +18426,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>283930.SH</t>
+          <t>524995.SZ</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -18249,49 +18435,53 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>3.5</v>
+        <v>11.0</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>30.74</v>
+      </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>26济南产业PPN002B</t>
+          <t>26川高K3</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>4.75Y</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>2.2911</t>
+          <t>1.7183</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>2.3000/--</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>济南产业发展投资集团有限公司</t>
+          <t>四川高速公路建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>C 26.50</t>
+          <t>C- 20.41</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -18301,7 +18491,7 @@
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 16:00</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr">
@@ -18318,12 +18508,12 @@
       <c r="V80" s="3"/>
       <c r="W80" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>2.08%~2.18%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
@@ -18334,17 +18524,17 @@
       <c r="Z80" s="3"/>
       <c r="AA80" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB80" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金7亿元拟用于偿还公司债券本金[24济产01]</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还有息债务,补充流动资金等法律法规允许的其他用途,具体用途根据发行人资金需求情况确定。</t>
         </is>
       </c>
       <c r="AC80" s="3" t="inlineStr">
         <is>
-          <t>中银国际证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,天府证券有限责任公司</t>
         </is>
       </c>
       <c r="AD80" s="3"/>
@@ -18360,17 +18550,17 @@
       </c>
       <c r="AG80" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH80" s="3" t="inlineStr">
         <is>
-          <t>济南产业发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>四川高速公路建设开发集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI80" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ80" s="3" t="inlineStr">
@@ -18400,32 +18590,32 @@
       </c>
       <c r="AO80" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP80" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ80" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR80" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS80" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT80" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU80" s="3" t="inlineStr">
@@ -18458,7 +18648,7 @@
     <row r="81" customHeight="true" ht="18.0">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>26川高K4</t>
+          <t>26漳九Y3</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -18468,62 +18658,62 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>524995.SZ</t>
+          <t>246034.SH</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>11.0</v>
+        <v>7.5</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H81" s="4" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>30.74</v>
+        <v>48.74</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>26川高K3</t>
+          <t>26漳九Y1</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>4.75Y</t>
+          <t>4.47Y+N</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>1.7183</t>
+          <t>1.8605</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>1.7600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司</t>
+          <t>漳州市九龙江集团有限公司</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>C- 20.41</t>
+          <t>B- 39.28</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -18550,12 +18740,12 @@
       <c r="V81" s="3"/>
       <c r="W81" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
@@ -18563,20 +18753,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z81" s="3"/>
+      <c r="Z81" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA81" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>福建省-漳州市</t>
         </is>
       </c>
       <c r="AB81" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还有息债务,补充流动资金等法律法规允许的其他用途,具体用途根据发行人资金需求情况确定。</t>
+          <t>本期债券募集资金在扣除发行费用后,拟用于偿还公司债券本金或置换已用于偿还到期公司债券本金的自有资金[23漳九Y1]</t>
         </is>
       </c>
       <c r="AC81" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,天府证券有限责任公司</t>
+          <t>中信证券股份有限公司,东兴证券股份有限公司,中信建投证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD81" s="3"/>
@@ -18592,12 +18786,12 @@
       </c>
       <c r="AG81" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH81" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第四期)</t>
+          <t>漳州市九龙江集团有限公司2026年面向专业投资者公开发行可续期公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI81" s="3" t="inlineStr">
@@ -18622,7 +18816,7 @@
       </c>
       <c r="AM81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN81" s="3" t="inlineStr">
@@ -18632,32 +18826,32 @@
       </c>
       <c r="AO81" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP81" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ81" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR81" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS81" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT81" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>医药商业</t>
         </is>
       </c>
       <c r="AU81" s="3" t="inlineStr">
@@ -18672,7 +18866,7 @@
       </c>
       <c r="AW81" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX81" s="3" t="inlineStr">
@@ -18690,7 +18884,7 @@
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>26漳九Y3</t>
+          <t>26淮开07</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -18700,47 +18894,47 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>246034.SH</t>
+          <t>283939.SH</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>7.5</v>
+        <v>8.65</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>48.74</v>
+        <v>38.74</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>26漳九Y1</t>
+          <t>26淮开05</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>4.47Y+N</t>
+          <t>2.94Y+2.00Y</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>1.8605</t>
+          <t>1.7197</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -18750,12 +18944,12 @@
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司</t>
+          <t>淮安开发控股有限公司</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>B- 39.28</t>
+          <t>C 25.33</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -18765,7 +18959,7 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>09-10 16:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr">
@@ -18782,37 +18976,33 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X82" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y82" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z82" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z82" s="3"/>
       <c r="AA82" s="3" t="inlineStr">
         <is>
-          <t>福建省-漳州市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB82" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟用于偿还公司债券本金或置换已用于偿还到期公司债券本金的自有资金[23漳九Y1]</t>
+          <t>本期债券的募集资金扣除发行费用后拟用于偿还发行人公司债券本金[23淮开06]</t>
         </is>
       </c>
       <c r="AC82" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,东兴证券股份有限公司,中信建投证券股份有限公司,华福证券股份有限公司</t>
+          <t>国信证券股份有限公司,中邮证券有限责任公司,中国银河证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD82" s="3"/>
@@ -18833,12 +19023,12 @@
       </c>
       <c r="AH82" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司2026年面向专业投资者公开发行可续期公司债券(第二期)(品种二)</t>
+          <t>淮安开发控股有限公司2026年面向专业投资者非公开发行公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI82" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ82" s="3" t="inlineStr">
@@ -18858,7 +19048,7 @@
       </c>
       <c r="AM82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN82" s="3" t="inlineStr">
@@ -18868,37 +19058,37 @@
       </c>
       <c r="AO82" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP82" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ82" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR82" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS82" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT82" s="3" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU82" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AV82" s="3" t="inlineStr">
@@ -18908,7 +19098,7 @@
       </c>
       <c r="AW82" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX82" s="3" t="inlineStr">
@@ -18926,7 +19116,7 @@
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>26淮开07</t>
+          <t>26风行K1</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -18936,47 +19126,39 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>283939.SH</t>
+          <t>283931.SH</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>8.65</v>
+        <v>3.0</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.80 ~ 3.00</t>
         </is>
       </c>
       <c r="H83" s="4" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>38.74</v>
+        <v>70.74</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>26淮开05</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>2.94Y+2.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3"/>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>1.7197</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
@@ -18986,14 +19168,10 @@
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>淮安开发控股有限公司</t>
-        </is>
-      </c>
-      <c r="P83" s="3" t="inlineStr">
-        <is>
-          <t>C 25.33</t>
-        </is>
-      </c>
+          <t>江苏风行天下创业投资有限公司</t>
+        </is>
+      </c>
+      <c r="P83" s="3"/>
       <c r="Q83" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -19016,38 +19194,34 @@
       </c>
       <c r="U83" s="3"/>
       <c r="V83" s="3"/>
-      <c r="W83" s="3" t="inlineStr">
-        <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X83" s="3" t="inlineStr">
-        <is>
-          <t>1.84%~1.94%</t>
-        </is>
-      </c>
-      <c r="Y83" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z83" s="3"/>
+      <c r="W83" s="3"/>
+      <c r="X83" s="3"/>
+      <c r="Y83" s="3"/>
+      <c r="Z83" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA83" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>江苏省-徐州市</t>
         </is>
       </c>
       <c r="AB83" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后拟用于偿还发行人公司债券本金[23淮开06]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将0.3亿元用于“年产30万吨Lyocell纤维项目”建设、1.8亿元用于偿还“年产30万吨Lyocell纤维项目”相关的有息债务,0.9亿元用于轻量化铝产业园项目建设。</t>
         </is>
       </c>
       <c r="AC83" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,中邮证券有限责任公司,中国银河证券股份有限公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD83" s="3"/>
+          <t>财达证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD83" s="3" t="inlineStr">
+        <is>
+          <t>中证信用融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE83" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -19065,7 +19239,7 @@
       </c>
       <c r="AH83" s="3" t="inlineStr">
         <is>
-          <t>淮安开发控股有限公司2026年面向专业投资者非公开发行公司债券(第五期)</t>
+          <t>江苏风行天下创业投资有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI83" s="3" t="inlineStr">
@@ -19090,7 +19264,7 @@
       </c>
       <c r="AM83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN83" s="3" t="inlineStr">
@@ -19100,47 +19274,43 @@
       </c>
       <c r="AO83" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP83" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP83" s="3"/>
       <c r="AQ83" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR83" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS83" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT83" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU83" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t/>
         </is>
       </c>
       <c r="AV83" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW83" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX83" s="3" t="inlineStr">
@@ -19158,7 +19328,7 @@
     <row r="84" customHeight="true" ht="18.0">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>26风行K1</t>
+          <t>26扬新03</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -19168,7 +19338,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>283931.SH</t>
+          <t>283820.SH</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -19177,43 +19347,55 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 3.00</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>70.74</v>
+        <v>63.74</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3"/>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>26扬新02</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>4.67Y</t>
+        </is>
+      </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.9914</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0000</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>江苏风行天下创业投资有限公司</t>
-        </is>
-      </c>
-      <c r="P84" s="3"/>
+          <t>扬州新材料投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>C- 17.70</t>
+        </is>
+      </c>
       <c r="Q84" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -19236,32 +19418,40 @@
       </c>
       <c r="U84" s="3"/>
       <c r="V84" s="3"/>
-      <c r="W84" s="3"/>
-      <c r="X84" s="3"/>
-      <c r="Y84" s="3"/>
-      <c r="Z84" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="W84" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X84" s="3" t="inlineStr">
+        <is>
+          <t>1.96%~2.06%</t>
+        </is>
+      </c>
+      <c r="Y84" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z84" s="3"/>
       <c r="AA84" s="3" t="inlineStr">
         <is>
-          <t>江苏省-徐州市</t>
+          <t>江苏省-扬州市</t>
         </is>
       </c>
       <c r="AB84" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将0.3亿元用于“年产30万吨Lyocell纤维项目”建设、1.8亿元用于偿还“年产30万吨Lyocell纤维项目”相关的有息债务,0.9亿元用于轻量化铝产业园项目建设。</t>
+          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还到期公司债券本金[23扬新03]</t>
         </is>
       </c>
       <c r="AC84" s="3" t="inlineStr">
         <is>
-          <t>财达证券股份有限公司</t>
+          <t>东吴证券股份有限公司,中国国际金融股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD84" s="3" t="inlineStr">
         <is>
-          <t>中证信用融资担保有限公司</t>
+          <t>扬州市兴仪投资控股集团有限公司</t>
         </is>
       </c>
       <c r="AE84" s="3" t="inlineStr">
@@ -19281,7 +19471,7 @@
       </c>
       <c r="AH84" s="3" t="inlineStr">
         <is>
-          <t>江苏风行天下创业投资有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+          <t>扬州新材料投资集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI84" s="3" t="inlineStr">
@@ -19316,28 +19506,32 @@
       </c>
       <c r="AO84" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP84" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP84" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ84" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR84" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS84" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT84" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU84" s="3" t="inlineStr">
@@ -19370,7 +19564,7 @@
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>26扬新03</t>
+          <t>26深投09</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -19380,7 +19574,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>283820.SH</t>
+          <t>524999.SZ</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -19389,53 +19583,53 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H85" s="4" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>63.74</v>
+        <v>28.74</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>26扬新02</t>
+          <t>26深投03</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>4.67Y</t>
+          <t>4.78Y</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>1.9914</t>
+          <t>1.7408</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>--/2.0000</t>
+          <t>--/1.7100</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>扬州新材料投资集团有限公司</t>
+          <t>深圳市投资控股有限公司</t>
         </is>
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>C- 17.70</t>
+          <t>C- 20.10</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -19462,40 +19656,40 @@
       <c r="V85" s="3"/>
       <c r="W85" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X85" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y85" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z85" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z85" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA85" s="3" t="inlineStr">
         <is>
-          <t>江苏省-扬州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB85" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还到期公司债券本金[23扬新03]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券[23深投05]</t>
         </is>
       </c>
       <c r="AC85" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,中国国际金融股份有限公司,光大证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD85" s="3" t="inlineStr">
-        <is>
-          <t>扬州市兴仪投资控股集团有限公司</t>
-        </is>
-      </c>
+          <t>国信证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD85" s="3"/>
       <c r="AE85" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -19508,17 +19702,17 @@
       </c>
       <c r="AG85" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH85" s="3" t="inlineStr">
         <is>
-          <t>扬州新材料投资集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种一)</t>
         </is>
       </c>
       <c r="AI85" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ85" s="3" t="inlineStr">
@@ -19538,7 +19732,7 @@
       </c>
       <c r="AM85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN85" s="3" t="inlineStr">
@@ -19548,32 +19742,32 @@
       </c>
       <c r="AO85" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP85" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ85" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR85" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS85" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT85" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU85" s="3" t="inlineStr">
@@ -19583,7 +19777,7 @@
       </c>
       <c r="AV85" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW85" s="3" t="inlineStr">
@@ -19606,7 +19800,7 @@
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>26深投09</t>
+          <t>26延安01</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -19616,7 +19810,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>524999.SZ</t>
+          <t>283970.SH</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -19625,53 +19819,53 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>28.74</v>
+        <v>76.74</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>26深投03</t>
+          <t>24延安04</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>4.78Y</t>
+          <t>5.25Y</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>1.7408</t>
+          <t>2.0543</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>--/1.7100</t>
+          <t>--/1.9000</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司</t>
+          <t>延安城市建设投资(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>C- 20.10</t>
+          <t>C 25.34</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -19681,7 +19875,7 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 14:00</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr">
@@ -19691,47 +19885,47 @@
       </c>
       <c r="T86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U86" s="3"/>
       <c r="V86" s="3"/>
       <c r="W86" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X86" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.23%~2.33%</t>
         </is>
       </c>
       <c r="Y86" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z86" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z86" s="3"/>
       <c r="AA86" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>陕西省-延安市</t>
         </is>
       </c>
       <c r="AB86" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券[23深投05]</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还到期的公司债券本金[23延安04,23延安05]</t>
         </is>
       </c>
       <c r="AC86" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD86" s="3"/>
+          <t>东兴证券股份有限公司,国投证券股份有限公司,西部证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD86" s="3" t="inlineStr">
+        <is>
+          <t>延安公用事业发展集团有限公司</t>
+        </is>
+      </c>
       <c r="AE86" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -19744,29 +19938,25 @@
       </c>
       <c r="AG86" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH86" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种一)</t>
+          <t>延安城市建设投资(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI86" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ86" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK86" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-11</t>
+        </is>
+      </c>
+      <c r="AK86" s="3"/>
       <c r="AL86" s="3" t="inlineStr">
         <is>
           <t/>
@@ -19779,17 +19969,17 @@
       </c>
       <c r="AN86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AO86" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP86" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ86" s="3" t="inlineStr">
@@ -19799,17 +19989,17 @@
       </c>
       <c r="AR86" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS86" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT86" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU86" s="3" t="inlineStr">
@@ -19819,7 +20009,7 @@
       </c>
       <c r="AV86" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW86" s="3" t="inlineStr">
@@ -19842,7 +20032,7 @@
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>26延安01</t>
+          <t>26安国01</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -19852,7 +20042,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>283970.SH</t>
+          <t>283907.SH</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -19861,7 +20051,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="inlineStr">
@@ -19870,46 +20060,42 @@
         </is>
       </c>
       <c r="H87" s="4" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>76.74</v>
+        <v>72.74</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>24延安04</t>
+          <t>26鹿工01</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>5.25Y</t>
+          <t>4.96Y</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>2.0543</t>
+          <t>1.9830</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>--/1.9000</t>
+          <t>2.0700/1.9600</t>
         </is>
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>延安城市建设投资(集团)有限责任公司</t>
-        </is>
-      </c>
-      <c r="P87" s="3" t="inlineStr">
-        <is>
-          <t>C 25.34</t>
-        </is>
-      </c>
+          <t>安阳市国控集团有限公司</t>
+        </is>
+      </c>
+      <c r="P87" s="3"/>
       <c r="Q87" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -19917,7 +20103,7 @@
       </c>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>09-10 14:00</t>
+          <t>09-10 15:00</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr">
@@ -19927,19 +20113,19 @@
       </c>
       <c r="T87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U87" s="3"/>
       <c r="V87" s="3"/>
       <c r="W87" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X87" s="3" t="inlineStr">
         <is>
-          <t>2.23%~2.33%</t>
+          <t>2.22%~2.32%</t>
         </is>
       </c>
       <c r="Y87" s="3" t="inlineStr">
@@ -19947,25 +20133,29 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z87" s="3"/>
+      <c r="Z87" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA87" s="3" t="inlineStr">
         <is>
-          <t>陕西省-延安市</t>
+          <t>河南省-安阳市</t>
         </is>
       </c>
       <c r="AB87" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还到期的公司债券本金[23延安04,23延安05]</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟使用2.00亿元偿还到期债务,3.185亿元用于固定资产投资项目建设,剩余不超过0.815亿元用于补充流动资金。</t>
         </is>
       </c>
       <c r="AC87" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司,国投证券股份有限公司,西部证券股份有限公司</t>
+          <t>国联民生证券承销保荐有限公司,万联证券股份有限公司,中邮证券有限责任公司</t>
         </is>
       </c>
       <c r="AD87" s="3" t="inlineStr">
         <is>
-          <t>延安公用事业发展集团有限公司</t>
+          <t>河南中豫信用增进有限公司</t>
         </is>
       </c>
       <c r="AE87" s="3" t="inlineStr">
@@ -19985,7 +20175,7 @@
       </c>
       <c r="AH87" s="3" t="inlineStr">
         <is>
-          <t>延安城市建设投资(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>安阳市国控集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI87" s="3" t="inlineStr">
@@ -19995,10 +20185,14 @@
       </c>
       <c r="AJ87" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
-        </is>
-      </c>
-      <c r="AK87" s="3"/>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK87" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL87" s="3" t="inlineStr">
         <is>
           <t/>
@@ -20006,24 +20200,20 @@
       </c>
       <c r="AM87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AO87" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP87" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP87" s="3"/>
       <c r="AQ87" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -20041,7 +20231,7 @@
       </c>
       <c r="AT87" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU87" s="3" t="inlineStr">
@@ -20074,7 +20264,7 @@
     <row r="88" customHeight="true" ht="18.0">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>26安国01</t>
+          <t>26绍金01</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -20084,60 +20274,64 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>283907.SH</t>
+          <t>283942.SH</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>72.74</v>
+        <v>55.94</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>26鹿工01</t>
+          <t>25绍兴金控PPN002</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>4.96Y</t>
+          <t>1.85Y</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>1.9830</t>
+          <t>1.7322</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>2.0700/1.9600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>安阳市国控集团有限公司</t>
-        </is>
-      </c>
-      <c r="P88" s="3"/>
+          <t>绍兴市金融控股有限公司</t>
+        </is>
+      </c>
+      <c r="P88" s="3" t="inlineStr">
+        <is>
+          <t>C 25.98</t>
+        </is>
+      </c>
       <c r="Q88" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -20145,7 +20339,7 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>09-10 15:00</t>
+          <t>09-10 16:00</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr">
@@ -20162,44 +20356,32 @@
       <c r="V88" s="3"/>
       <c r="W88" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X88" s="3" t="inlineStr">
-        <is>
-          <t>2.22%~2.32%</t>
-        </is>
-      </c>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X88" s="3"/>
       <c r="Y88" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z88" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z88" s="3"/>
       <c r="AA88" s="3" t="inlineStr">
         <is>
-          <t>河南省-安阳市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB88" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟使用2.00亿元偿还到期债务,3.185亿元用于固定资产投资项目建设,剩余不超过0.815亿元用于补充流动资金。</t>
+          <t>本期债券拟募集资金规模不超过10亿元(含10亿元),扣除发行费用后,拟用于偿还到期公司债券[金控KY01,金控KY02]</t>
         </is>
       </c>
       <c r="AC88" s="3" t="inlineStr">
         <is>
-          <t>国联民生证券承销保荐有限公司,万联证券股份有限公司,中邮证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD88" s="3" t="inlineStr">
-        <is>
-          <t>河南中豫信用增进有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD88" s="3"/>
       <c r="AE88" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -20217,7 +20399,7 @@
       </c>
       <c r="AH88" s="3" t="inlineStr">
         <is>
-          <t>安阳市国控集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>绍兴市金融控股有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI88" s="3" t="inlineStr">
@@ -20227,14 +20409,10 @@
       </c>
       <c r="AJ88" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK88" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-14</t>
+        </is>
+      </c>
+      <c r="AK88" s="3"/>
       <c r="AL88" s="3" t="inlineStr">
         <is>
           <t/>
@@ -20252,30 +20430,34 @@
       </c>
       <c r="AO88" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP88" s="3"/>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP88" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ88" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR88" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AS88" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AT88" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR88" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS88" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT88" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
       <c r="AU88" s="3" t="inlineStr">
         <is>
           <t/>
@@ -20283,7 +20465,7 @@
       </c>
       <c r="AV88" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW88" s="3" t="inlineStr">
@@ -20306,57 +20488,59 @@
     <row r="89" customHeight="true" ht="18.0">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>26绍金01</t>
+          <t>26太仓水务MTN003</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>09-10 19:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>283942.SH</t>
+          <t>102683598.IB</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F89" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H89" s="4" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>55.94</v>
+        <v>52.94</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>25绍兴金控PPN002</t>
+          <t>24太仓水务MTN002</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>1.85Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>1.7322</t>
+          <t>1.7376</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -20366,12 +20550,12 @@
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>绍兴市金融控股有限公司</t>
+          <t>太仓市水务集团有限公司</t>
         </is>
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>C 25.98</t>
+          <t>C- 12.09</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -20381,7 +20565,7 @@
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>09-10 16:00</t>
+          <t>09-10 09:00</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr">
@@ -20391,17 +20575,25 @@
       </c>
       <c r="T89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="U89" s="3"/>
-      <c r="V89" s="3"/>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U89" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V89" s="4" t="n">
+        <v>13.0</v>
+      </c>
       <c r="W89" s="3" t="inlineStr">
         <is>
           <t>6+</t>
         </is>
       </c>
-      <c r="X89" s="3"/>
+      <c r="X89" s="3" t="inlineStr">
+        <is>
+          <t>1.83%~1.93%</t>
+        </is>
+      </c>
       <c r="Y89" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -20410,23 +20602,23 @@
       <c r="Z89" s="3"/>
       <c r="AA89" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB89" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟募集资金规模不超过10亿元(含10亿元),扣除发行费用后,拟用于偿还到期公司债券[金控KY01,金控KY02]</t>
+          <t>本期中期票据募集资金2亿元，发行人计划将募集资金全部用于偿还到期的有息负债。</t>
         </is>
       </c>
       <c r="AC89" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>中信银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD89" s="3"/>
       <c r="AE89" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF89" s="3" t="inlineStr">
@@ -20436,96 +20628,98 @@
       </c>
       <c r="AG89" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH89" s="3" t="inlineStr">
         <is>
-          <t>绍兴市金融控股有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>太仓市水务集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI89" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ89" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK89" s="3"/>
       <c r="AL89" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM89" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN89" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO89" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP89" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ89" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR89" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AS89" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AT89" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU89" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM89" s="3" t="inlineStr">
+      <c r="AV89" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW89" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AX89" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY89" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AN89" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO89" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP89" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ89" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR89" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AS89" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AT89" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU89" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV89" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW89" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX89" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY89" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AZ89" s="3"/>
+      <c r="AZ89" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
